--- a/vehicle_inspection_forms/048_vehicle_appraisal_form--vehicle_inspection_forms.xlsx
+++ b/vehicle_inspection_forms/048_vehicle_appraisal_form--vehicle_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2078,17 +2078,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>interior_choices</t>
+          <t>exterior_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2-door</t>
+          <t>1-door</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2-door</t>
+          <t>1-door</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1-door</t>
+          <t>2-doors</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1-door</t>
+          <t>2-doors</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2-doors</t>
+          <t>3-doors</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2-doors</t>
+          <t>3-doors</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3-doors</t>
+          <t>4-door</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3-doors</t>
+          <t>4-door</t>
         </is>
       </c>
     </row>
@@ -2151,29 +2151,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4-door</t>
+          <t>6-doors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>4-door</t>
+          <t>6-doors</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>exterior_choices</t>
+          <t>drive_train_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6-doors</t>
+          <t>2-wheel</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6-doors</t>
+          <t>2-wheel</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2-wheel</t>
+          <t>4-wheel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2-wheel</t>
+          <t>4-wheel</t>
         </is>
       </c>
     </row>
@@ -2202,29 +2202,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4-wheel</t>
+          <t>all-wheel_drive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4-wheel</t>
+          <t>All-Wheel Drive</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>drive_train_choices</t>
+          <t>drive_side_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>all-wheel_drive</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>All-Wheel Drive</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2253,29 +2253,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>rear</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Rear</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>drive_side_choices</t>
+          <t>fuel_type_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>rear</t>
+          <t>petrol</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rear</t>
+          <t>Petrol</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>petrol</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Petrol</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>diesel</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -2338,27 +2338,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gasoline</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
-        <is>
-          <t>Gasoline</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_type_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
         <is>
           <t>Electric</t>
         </is>
